--- a/便マスター.xlsx
+++ b/便マスター.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>便ID</t>
   </si>
@@ -172,6 +172,9 @@
     <t>便マスター更新者</t>
   </si>
   <si>
+    <t>便枝連番</t>
+  </si>
+  <si>
     <t>便枝番ID</t>
   </si>
   <si>
@@ -199,40 +202,76 @@
     <t>便枝番マスター更新者</t>
   </si>
   <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
     <t>03:40</t>
   </si>
   <si>
     <t>04:10</t>
   </si>
   <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>22:40</t>
+    <t>16:49</t>
+  </si>
+  <si>
+    <t>17:39</t>
+  </si>
+  <si>
+    <t>2024/01/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2024/07/28 23:59:00</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>23:19</t>
+  </si>
+  <si>
+    <t>23:49</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>06:09</t>
   </si>
   <si>
     <t>05:50</t>
@@ -241,52 +280,16 @@
     <t>06:10</t>
   </si>
   <si>
+    <t>07:59</t>
+  </si>
+  <si>
+    <t>08:39</t>
+  </si>
+  <si>
     <t>08:00</t>
   </si>
   <si>
     <t>08:40</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>2024/01/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2024/07/28 23:59:00</t>
-  </si>
-  <si>
-    <t>07:59</t>
-  </si>
-  <si>
-    <t>08:39</t>
-  </si>
-  <si>
-    <t>16:49</t>
-  </si>
-  <si>
-    <t>17:39</t>
-  </si>
-  <si>
-    <t>23:19</t>
-  </si>
-  <si>
-    <t>23:49</t>
   </si>
 </sst>
 </file>
@@ -573,7 +576,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,6 +643,9 @@
       <c r="U1" s="0" t="s">
         <v>59</v>
       </c>
+      <c r="V1" s="0" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
@@ -681,28 +687,31 @@
       <c r="M2" s="0">
         <v>1</v>
       </c>
-      <c r="N2" s="0" t="s">
-        <v>60</v>
+      <c r="N2" s="0">
+        <v>2</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>61</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S2" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T2" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U2" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -746,28 +755,31 @@
       <c r="M3" s="0">
         <v>2</v>
       </c>
-      <c r="N3" s="0" t="s">
-        <v>62</v>
+      <c r="N3" s="0">
+        <v>3</v>
       </c>
       <c r="O3" s="0" t="s">
         <v>63</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T3" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -811,28 +823,31 @@
       <c r="M4" s="0">
         <v>3</v>
       </c>
-      <c r="N4" s="0" t="s">
-        <v>64</v>
+      <c r="N4" s="0">
+        <v>4</v>
       </c>
       <c r="O4" s="0" t="s">
         <v>65</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T4" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V4" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -876,28 +891,31 @@
       <c r="M5" s="0">
         <v>4</v>
       </c>
-      <c r="N5" s="0" t="s">
-        <v>66</v>
+      <c r="N5" s="0">
+        <v>5</v>
       </c>
       <c r="O5" s="0" t="s">
         <v>67</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V5" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -941,28 +959,31 @@
       <c r="M6" s="0">
         <v>5</v>
       </c>
-      <c r="N6" s="0" t="s">
-        <v>68</v>
+      <c r="N6" s="0">
+        <v>6</v>
       </c>
       <c r="O6" s="0" t="s">
         <v>69</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S6" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T6" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U6" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V6" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1006,28 +1027,31 @@
       <c r="M7" s="0">
         <v>6</v>
       </c>
-      <c r="N7" s="0" t="s">
-        <v>70</v>
+      <c r="N7" s="0">
+        <v>1</v>
       </c>
       <c r="O7" s="0" t="s">
         <v>71</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T7" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U7" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V7" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1069,30 +1093,33 @@
         <v>31</v>
       </c>
       <c r="M8" s="0">
-        <v>7</v>
-      </c>
-      <c r="N8" s="0" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="N8" s="0">
+        <v>19</v>
       </c>
       <c r="O8" s="0" t="s">
         <v>73</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="Q8" s="0" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="R8" s="0" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T8" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U8" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V8" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1134,30 +1161,33 @@
         <v>31</v>
       </c>
       <c r="M9" s="0">
-        <v>8</v>
-      </c>
-      <c r="N9" s="0" t="s">
-        <v>74</v>
+        <v>2</v>
+      </c>
+      <c r="N9" s="0">
+        <v>9</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="Q9" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R9" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S9" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T9" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U9" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V9" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1199,30 +1229,33 @@
         <v>31</v>
       </c>
       <c r="M10" s="0">
-        <v>9</v>
-      </c>
-      <c r="N10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="0">
+        <v>20</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="P10" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q10" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="R10" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="O10" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="P10" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q10" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="R10" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="S10" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T10" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U10" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V10" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1264,30 +1297,33 @@
         <v>31</v>
       </c>
       <c r="M11" s="0">
+        <v>4</v>
+      </c>
+      <c r="N11" s="0">
         <v>10</v>
       </c>
-      <c r="N11" s="0" t="s">
-        <v>78</v>
-      </c>
       <c r="O11" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="Q11" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R11" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U11" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V11" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1329,30 +1365,33 @@
         <v>31</v>
       </c>
       <c r="M12" s="0">
-        <v>17</v>
-      </c>
-      <c r="N12" s="0" t="s">
-        <v>80</v>
+        <v>5</v>
+      </c>
+      <c r="N12" s="0">
+        <v>17</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q12" s="0" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T12" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V12" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1394,30 +1433,33 @@
         <v>31</v>
       </c>
       <c r="M13" s="0">
-        <v>18</v>
-      </c>
-      <c r="N13" s="0" t="s">
-        <v>84</v>
+        <v>6</v>
+      </c>
+      <c r="N13" s="0">
+        <v>7</v>
       </c>
       <c r="O13" s="0" t="s">
         <v>85</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q13" s="0" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="R13" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T13" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U13" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V13" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1459,30 +1501,33 @@
         <v>31</v>
       </c>
       <c r="M14" s="0">
-        <v>19</v>
-      </c>
-      <c r="N14" s="0" t="s">
-        <v>86</v>
+        <v>7</v>
+      </c>
+      <c r="N14" s="0">
+        <v>18</v>
       </c>
       <c r="O14" s="0" t="s">
         <v>87</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Q14" s="0" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T14" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U14" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V14" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1524,30 +1569,33 @@
         <v>31</v>
       </c>
       <c r="M15" s="0">
-        <v>20</v>
-      </c>
-      <c r="N15" s="0" t="s">
-        <v>88</v>
+        <v>8</v>
+      </c>
+      <c r="N15" s="0">
+        <v>8</v>
       </c>
       <c r="O15" s="0" t="s">
         <v>89</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="Q15" s="0" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="R15" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S15" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T15" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U15" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="V15" s="0" t="s">
         <v>20</v>
       </c>
     </row>
